--- a/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (11)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (19)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF10B65-3071-4DCF-B829-A0A457EFE0D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7171DFB3-7245-40CA-B310-22F175716619}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,12 +76,6 @@
     <t>备件好还率得分</t>
   </si>
   <si>
-    <t>满意度回访权重</t>
-  </si>
-  <si>
-    <t>满意度回访得分</t>
-  </si>
-  <si>
     <t>APM开单率权重</t>
   </si>
   <si>
@@ -98,6 +92,12 @@
   </si>
   <si>
     <t>工程师配置得分</t>
+  </si>
+  <si>
+    <t>顾客满意度回访权重</t>
+  </si>
+  <si>
+    <t>顾客满意度回访得分</t>
   </si>
 </sst>
 </file>
@@ -464,34 +464,34 @@
         <v>15</v>
       </c>
       <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" t="s">
         <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" t="s">
-        <v>18</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N1" t="s">
         <v>4</v>
       </c>
       <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>21</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (19)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\kpi模板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7171DFB3-7245-40CA-B310-22F175716619}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BB366E-C3F9-4826-B110-F450CED437E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>租户</t>
   </si>
@@ -68,12 +68,6 @@
   </si>
   <si>
     <t>备件归还得分</t>
-  </si>
-  <si>
-    <t>备件好还率权重</t>
-  </si>
-  <si>
-    <t>备件好还率得分</t>
   </si>
   <si>
     <t>APM开单率权重</t>
@@ -415,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
@@ -424,21 +418,19 @@
     <col min="4" max="4" width="15.5546875" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="33.5546875" customWidth="1"/>
-    <col min="7" max="7" width="40.5546875" customWidth="1"/>
-    <col min="8" max="8" width="43" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="26.6640625" customWidth="1"/>
-    <col min="11" max="11" width="25.5546875" customWidth="1"/>
-    <col min="12" max="12" width="38.77734375" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="21.33203125" customWidth="1"/>
-    <col min="15" max="15" width="26.5546875" customWidth="1"/>
-    <col min="16" max="16" width="20.77734375" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" customWidth="1"/>
-    <col min="18" max="18" width="29.21875" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" customWidth="1"/>
+    <col min="9" max="9" width="25.5546875" customWidth="1"/>
+    <col min="10" max="10" width="38.77734375" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" customWidth="1"/>
+    <col min="13" max="13" width="26.5546875" customWidth="1"/>
+    <col min="14" max="14" width="20.77734375" customWidth="1"/>
+    <col min="15" max="15" width="28.6640625" customWidth="1"/>
+    <col min="16" max="16" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -458,40 +450,34 @@
         <v>13</v>
       </c>
       <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>17</v>
-      </c>
-      <c r="N1" t="s">
-        <v>4</v>
       </c>
       <c r="O1" t="s">
         <v>18</v>
       </c>
       <c r="P1" t="s">
         <v>19</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\kpi模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BB366E-C3F9-4826-B110-F450CED437E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F156C561-60FA-409C-B627-A0437938D71E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>租户</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>顾客满意度回访得分</t>
+  </si>
+  <si>
+    <t>名次</t>
   </si>
 </sst>
 </file>
@@ -409,28 +412,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="33.5546875" customWidth="1"/>
-    <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="26.6640625" customWidth="1"/>
-    <col min="9" max="9" width="25.5546875" customWidth="1"/>
-    <col min="10" max="10" width="38.77734375" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" customWidth="1"/>
-    <col min="13" max="13" width="26.5546875" customWidth="1"/>
-    <col min="14" max="14" width="20.77734375" customWidth="1"/>
-    <col min="15" max="15" width="28.6640625" customWidth="1"/>
-    <col min="16" max="16" width="29.21875" customWidth="1"/>
+    <col min="3" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="33.5546875" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" customWidth="1"/>
+    <col min="11" max="11" width="38.77734375" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" customWidth="1"/>
+    <col min="14" max="14" width="26.5546875" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" customWidth="1"/>
+    <col min="16" max="16" width="28.6640625" customWidth="1"/>
+    <col min="17" max="17" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -441,42 +444,45 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (3)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F156C561-60FA-409C-B627-A0437938D71E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F1E23F-A8CF-4F56-80C6-AD9B1D36EDA6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>租户</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>名次</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -412,77 +415,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="33.5546875" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" customWidth="1"/>
-    <col min="10" max="10" width="25.5546875" customWidth="1"/>
-    <col min="11" max="11" width="38.77734375" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
-    <col min="13" max="13" width="21.33203125" customWidth="1"/>
-    <col min="14" max="14" width="26.5546875" customWidth="1"/>
-    <col min="15" max="15" width="20.77734375" customWidth="1"/>
-    <col min="16" max="16" width="28.6640625" customWidth="1"/>
-    <col min="17" max="17" width="29.21875" customWidth="1"/>
+    <col min="1" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="33.5546875" customWidth="1"/>
+    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="10" max="10" width="26.6640625" customWidth="1"/>
+    <col min="11" max="11" width="25.5546875" customWidth="1"/>
+    <col min="12" max="12" width="38.77734375" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="21.33203125" customWidth="1"/>
+    <col min="15" max="15" width="26.5546875" customWidth="1"/>
+    <col min="16" max="16" width="20.77734375" customWidth="1"/>
+    <col min="17" max="17" width="28.6640625" customWidth="1"/>
+    <col min="18" max="18" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
       <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -494,37 +500,40 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13DA27F-EA07-447A-A76F-1EFE02F9A626}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="36.5546875" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="6" width="21.5546875" customWidth="1"/>
-    <col min="7" max="7" width="27.33203125" customWidth="1"/>
+    <col min="1" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" customWidth="1"/>
+    <col min="4" max="4" width="36.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="7" width="21.5546875" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/keyHehaviorIndex/Key_Behavior_Index_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaCodes\company\hc-apm-web\src\src\main\webapp\portal\zkb\keyHehaviorIndex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F1E23F-A8CF-4F56-80C6-AD9B1D36EDA6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127EC3D9-BFB6-46BF-AAB5-BA43BFC61B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Key_Behavior_Index_List" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>租户</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>DI名次</t>
+  </si>
+  <si>
+    <t>CCS名次</t>
+  </si>
+  <si>
+    <t>PCB名次</t>
   </si>
 </sst>
 </file>
@@ -137,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -415,28 +424,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="33.5546875" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="26.6640625" customWidth="1"/>
-    <col min="11" max="11" width="25.5546875" customWidth="1"/>
-    <col min="12" max="12" width="38.77734375" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="21.33203125" customWidth="1"/>
-    <col min="15" max="15" width="26.5546875" customWidth="1"/>
-    <col min="16" max="16" width="20.77734375" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" customWidth="1"/>
-    <col min="18" max="18" width="29.21875" customWidth="1"/>
+    <col min="1" max="2" width="21.1015625" customWidth="1"/>
+    <col min="3" max="3" width="12.89453125" customWidth="1"/>
+    <col min="4" max="4" width="11.68359375" customWidth="1"/>
+    <col min="5" max="5" width="15.5234375" customWidth="1"/>
+    <col min="6" max="9" width="11.68359375" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="33.5234375" customWidth="1"/>
+    <col min="12" max="12" width="33" customWidth="1"/>
+    <col min="13" max="13" width="26.68359375" customWidth="1"/>
+    <col min="14" max="14" width="25.5234375" customWidth="1"/>
+    <col min="15" max="15" width="38.7890625" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="21.3125" customWidth="1"/>
+    <col min="18" max="18" width="26.5234375" customWidth="1"/>
+    <col min="19" max="19" width="20.7890625" customWidth="1"/>
+    <col min="20" max="20" width="28.68359375" customWidth="1"/>
+    <col min="21" max="21" width="29.20703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -450,45 +460,54 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
       <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -501,17 +520,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13DA27F-EA07-447A-A76F-1EFE02F9A626}">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="31.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="7" width="21.5546875" customWidth="1"/>
-    <col min="8" max="8" width="27.33203125" customWidth="1"/>
+    <col min="1" max="2" width="31.3125" customWidth="1"/>
+    <col min="3" max="3" width="24.7890625" customWidth="1"/>
+    <col min="4" max="4" width="36.5234375" customWidth="1"/>
+    <col min="5" max="5" width="21.68359375" customWidth="1"/>
+    <col min="6" max="7" width="21.5234375" customWidth="1"/>
+    <col min="8" max="8" width="27.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>10</v>
       </c>
